--- a/solution.xlsx
+++ b/solution.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>103</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -461,7 +461,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -481,7 +481,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -501,7 +501,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -515,46 +515,6 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>0500000005</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>0500000006</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
         <v>1</v>
       </c>
     </row>

--- a/solution.xlsx
+++ b/solution.xlsx
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>User A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>101</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -461,7 +461,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>User B</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -481,7 +481,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>User C</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -501,7 +501,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>User D</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">

--- a/solution.xlsx
+++ b/solution.xlsx
@@ -441,12 +441,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>User A</t>
+          <t>U1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0500000001</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -461,12 +461,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>User B</t>
+          <t>U2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0500000002</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -481,12 +481,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>User C</t>
+          <t>U3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0500000003</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -501,12 +501,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>User D</t>
+          <t>U4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0500000004</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
